--- a/dist_actualizado/Portafolio.xlsx
+++ b/dist_actualizado/Portafolio.xlsx
@@ -632,12 +632,12 @@
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Recaudo impuestos</t>
+          <t>Gobierno De La Espriella radica proyecto de Presupuesto</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/economia/impuestos/recaudo-de-impuestos-crece-9-4-anual-pero-expertos-revisan-ritmo-de-cumplimiento-fiscal-498278</t>
+          <t>https://www.portafolio.co/economia/gobierno-de-la-espriella-radica-proyecto-de-presupuesto-por-un-monto-de-634-9-billones-501302</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -647,17 +647,17 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15  3:08 PM</t>
+          <t>2026-08-27  3:39 PM</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/amp/economia/impuestos/recaudo-de-impuestos-crece-9-4-anual-pero-expertos-revisan-ritmo-de-cumplimiento-fiscal-498278</t>
+          <t>https://www.portafolio.co/amp/economia/gobierno-de-la-espriella-radica-proyecto-de-presupuesto-por-un-monto-de-634-9-billones-501302</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>Anif señala que el recaudo neto quedó $0,1 billones por debajo de la meta acumulada.</t>
+          <t>El proyecto que se devolvió fue presentado por un monto de $575 billones. Es decir, un aumento de $59,9 billones.</t>
         </is>
       </c>
     </row>
@@ -665,32 +665,32 @@
       <c r="A3" s="9" t="inlineStr"/>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Proyectos busca</t>
+          <t>Colombia podría multiplicar por 70 sus reservas de gas</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/energia/y-los-proyectos-que-busca-destrabar-colombia-para-enfrentar-el-deficit-de-gas-natural-esto-es-lo-que-debe-saber-498271</t>
+          <t>https://www.portafolio.co/energia/colombia-podria-multiplicar-por-70-sus-reservas-de-gas-pero-lleva-12-anos-dandole-vueltas-al-fracking-campetrol-501316</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Energía, sostenibilidad, opinión</t>
+          <t>Energía, sostenibilidad</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15  1:53 PM</t>
+          <t>2026-08-27  3:26 PM</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/amp/energia/y-los-proyectos-que-busca-destrabar-colombia-para-enfrentar-el-deficit-de-gas-natural-esto-es-lo-que-debe-saber-498271</t>
+          <t>https://www.portafolio.co/amp/energia/colombia-podria-multiplicar-por-70-sus-reservas-de-gas-pero-lleva-12-anos-dandole-vueltas-al-fracking-campetrol-501316</t>
         </is>
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>La caída de la producción obliga al país a importar más mientras avanzan proyectos clave en tierra y costa afuera.</t>
+          <t>El presidente del gremio pide acelerar los no convencionales y la exploración para recuperar el sector.</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Banco AV</t>
+          <t>Imparten nuevas reglas a bancos sobre créditos vigentes plazos</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/mis-finanzas/creditos/banco-av-villas-premia-a-los-hinchas-de-santa-fe-y-millonarios-con-beneficios-498269</t>
+          <t>https://www.portafolio.co/mis-finanzas/creditos/imparten-nuevas-reglas-a-bancos-sobre-creditos-vigentes-plazos-y-condiciones-de-pago-para-afectados-por-terremoto-501314</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15  1:45 PM</t>
+          <t>2026-08-27  3:25 PM</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/amp/mis-finanzas/creditos/banco-av-villas-premia-a-los-hinchas-de-santa-fe-y-millonarios-con-beneficios-498269</t>
+          <t>https://www.portafolio.co/amp/mis-finanzas/creditos/imparten-nuevas-reglas-a-bancos-sobre-creditos-vigentes-plazos-y-condiciones-de-pago-para-afectados-por-terremoto-501314</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>Los seguidores con la tarjeta de crédito del 'León' o el 'Embajador' tienen descuento en la compra de abonos.</t>
+          <t>Los plazos no podrán exceder los 20 años. Las nuevas órdenes fueron impartidas por la Superfinanciera.</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,12 @@
       <c r="A5" s="9" t="inlineStr"/>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Petróleo sube</t>
+          <t>Latam reabre la ruta Bogotá Caracas tras el terremoto</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/internacional/petroleo-sube-tras-nuevos-ataques-de-estados-unidos-contra-objetivos-militares-en-iran-498257</t>
+          <t>https://www.portafolio.co/internacional/latam-reabre-la-ruta-bogota-caracas-tras-el-terremoto-en-venezuela-vuelos-iniciaran-desde-el-4-de-septiembre-501300</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>2026-07-15  11:43 AM</t>
+          <t>2026-08-27  12:36 PM</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/amp/internacional/petroleo-sube-tras-nuevos-ataques-de-estados-unidos-contra-objetivos-militares-en-iran-498257</t>
+          <t>https://www.portafolio.co/amp/internacional/latam-reabre-la-ruta-bogota-caracas-tras-el-terremoto-en-venezuela-vuelos-iniciaran-desde-el-4-de-septiembre-501300</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>Los mercados petroleros siguen reaccionando a nueva ofensiva estadounidense en el Golfo Pérsico.</t>
+          <t>La operación funcionará los lunes, viernes y sábados, con salida desde Bogotá programada a las 7:35.</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nuevo capítulo</t>
+          <t>Eclipse lunar de hoy 27 de agosto</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/tendencias/sociales/nuevo-capitulo-de-betty-la-fea-hijas-de-fernando-gaitan-demandaron-por-los-derechos-de-streaming-498241</t>
+          <t>https://www.portafolio.co/tendencias/sociales/eclipse-lunar-de-hoy-27-de-agosto-hora-exacta-y-guia-para-verlo-desde-cualquier-ciudad-colombiana-501299</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
@@ -779,17 +779,17 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15  8:38 AM</t>
+          <t>2026-08-27  12:02 PM</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>https://www.portafolio.co/amp/tendencias/sociales/nuevo-capitulo-de-betty-la-fea-hijas-de-fernando-gaitan-demandaron-por-los-derechos-de-streaming-498241</t>
+          <t>https://www.portafolio.co/amp/tendencias/sociales/eclipse-lunar-de-hoy-27-de-agosto-hora-exacta-y-guia-para-verlo-desde-cualquier-ciudad-colombiana-501299</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Las herederas del libretista dicen que los contratos originales solo autorizaban la emisión por televisión abierta.</t>
+          <t>El fenómeno cubrirá el 96,3% de la Luna en su máximo y podrá seguirse a simple vista en todo el territorio.</t>
         </is>
       </c>
     </row>
